--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,6 +882,46 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:08:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baseline </t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet34 encoder)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>39</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9467</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8938</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Baseline for reference</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,46 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-14 23:24:44</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>lower_epochs_1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9025</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9088000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8342000000000001</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20 epochs using lr=2e-5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,6 +962,46 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-14 23:50:53</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lower_epochs_2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9086</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8411</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30 epochs using lr=2e-5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,6 +1002,46 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-15 00:01:44</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lower_epochs_3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>40</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9254</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9118000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8393</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>40 epochs using lr=2e-5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,6 +1042,46 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-15 13:54:34</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>augmentation_run_1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9271</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9196</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8522</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>flip + rotate augmentation, lr=2e-5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,14 +485,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:58:26</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>46125</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>augmentation_run_1</t>
+          <t>pre_fine_tuning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -497,26 +499,426 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8639</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8937</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>baseline before fine-tuning</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-13 17:31:22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fine_tune_run_1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>50</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.2358</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9271</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9196</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.8522</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>flip + rotate augmentation, lr=2e-5</t>
+      <c r="E3" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9189000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9139</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9161</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8461</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>pretrained, frozen backbone then unfrozen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-13 17:48:55</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fine_tune_run_2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9177</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9145</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8435</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>using optimiser lr=1e-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-13 18:04:16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fine_tune_run_3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9146</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9162</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9152</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8445</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>using optimiser lr=5e-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-13 18:16:07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fine_tune_run_4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9212</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9124</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9165</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8468</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>using optimiser lr=2e-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-13 18:47:43</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fine_tune_run_5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9083</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9222</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8443000000000001</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BCE and Dice</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-13 19:06:27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fine_tune_run_6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9242</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9063</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9149</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>combined tversky loss @ alpha=0.5, beta=0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-13 19:18:18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fine_tune_run_6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9215</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9104</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9156</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.8454</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>combined tversky loss @ alpha=0.3, beta=0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-13 19:30:13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fine_tune_run_7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9293</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8977000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8408</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>combined tversky loss @ alpha=0.7, beta=0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-13 19:41:48</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fine_tune_run_8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9215</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9136</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8419</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>combined tversky loss @ alpha=0.6, beta=0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:08:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baseline </t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet34 encoder)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>39</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9467</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8938</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Baseline for reference</t>
         </is>
       </c>
     </row>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,46 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:07:08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>augmentation_run_1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9271</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9196</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8522</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>flip + rotate augmentation, lr=2e-5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,6 +962,46 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:25:06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>augmentation_run_2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9118000000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9172</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8481</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>flip + rotate augmentation, lr=1e-5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,6 +1002,46 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>augmentation_brightness_run_1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9233</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9203</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8532999999999999</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>flip + rotate + mild brightness/contrast augmentation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,6 +1042,46 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-15 15:18:48</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>augmentation_brightness_checkpoint_run_1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2433</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9393</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8544</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>flip + rotate + mild brightness/contrast augmentation, best checkpoint by val IoU at epoch 50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cm/training_results_history.xlsx
+++ b/cm/training_results_history.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,46 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-15 15:52:22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>augmentation_brightness_checkpoint_run_2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DeepLabV3_ResNet50</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9136</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9213</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8549</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>flip + rotate + mild brightness/contrast augmentation, best checkpoint by val IoU at epoch 36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
